--- a/tables/sensor_summary.xlsx
+++ b/tables/sensor_summary.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82A5FCE-45E0-8E45-B387-FB583EAED619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A90B58-9053-9C4B-9163-D6D7772010E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28460" yWindow="1420" windowWidth="28680" windowHeight="18040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13520" yWindow="6060" windowWidth="28680" windowHeight="18040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="csiem_data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="light" sheetId="1" r:id="rId1"/>
+    <sheet name="wq" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="187">
   <si>
     <t>Table</t>
   </si>
@@ -52,6 +52,9 @@
     <t>WAMSI-WWMSP3-SEDDEP</t>
   </si>
   <si>
+    <t>Turbidity</t>
+  </si>
+  <si>
     <t>SiteID</t>
   </si>
   <si>
@@ -169,9 +172,6 @@
     <t>S4S2</t>
   </si>
   <si>
-    <t>DWER (Profiling)</t>
-  </si>
-  <si>
     <t>North CS4</t>
   </si>
   <si>
@@ -184,9 +184,6 @@
     <t>Desal</t>
   </si>
   <si>
-    <t>DWER (Original)</t>
-  </si>
-  <si>
     <t>Eastern Margin SG</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>Westport</t>
   </si>
   <si>
-    <t>DWER (Re-configured)</t>
-  </si>
-  <si>
     <t>SurfaceWESTPORTS</t>
   </si>
   <si>
@@ -358,12 +352,6 @@
     <t>hillarysish</t>
   </si>
   <si>
-    <t>SPOT-</t>
-  </si>
-  <si>
-    <t>Hilarys</t>
-  </si>
-  <si>
     <t>GK-41870</t>
   </si>
   <si>
@@ -409,24 +397,6 @@
     <t>2020-12 - 2021-11</t>
   </si>
   <si>
-    <t>2022-05 - 2023-04</t>
-  </si>
-  <si>
-    <t>Not QC'ed raw data handover. 1xMS9 bottom deployment</t>
-  </si>
-  <si>
-    <t>2021-05 - 2023-05</t>
-  </si>
-  <si>
-    <t>2020-12 - 2023-05</t>
-  </si>
-  <si>
-    <t>2021-09 - 2023-05</t>
-  </si>
-  <si>
-    <t>2021-09 - 2023-01</t>
-  </si>
-  <si>
     <t>2020-12 - 2024-12</t>
   </si>
   <si>
@@ -488,6 +458,135 @@
   </si>
   <si>
     <t>DWER-CSMOORING-MS9B</t>
+  </si>
+  <si>
+    <t>WaterQuality</t>
+  </si>
+  <si>
+    <t>Not QC'ed raw data handover. 1xEXO2 profiling deployment (2.5 - 17.5m)</t>
+  </si>
+  <si>
+    <t>2020-12 - 2022-12</t>
+  </si>
+  <si>
+    <t>Not QC'ed raw data handover. 1xEXO2 + 1xMS9 hourly profiling deployment (2.5 - 17.5m)</t>
+  </si>
+  <si>
+    <t>2020-12 - 2023-01</t>
+  </si>
+  <si>
+    <t>QC Level 2 post reconfiguration data. 1xEXO2 bottom deployment</t>
+  </si>
+  <si>
+    <t>2023-10 - 2024-12</t>
+  </si>
+  <si>
+    <t>QC Level 2 post reconfiguration data. 1xEXO2 surface deployment</t>
+  </si>
+  <si>
+    <t>2024-11 - 2024-12</t>
+  </si>
+  <si>
+    <t>2023-05 - 2024-12</t>
+  </si>
+  <si>
+    <t>2023-07 - 2024-12</t>
+  </si>
+  <si>
+    <t>Salinity</t>
+  </si>
+  <si>
+    <t>Oxygen</t>
+  </si>
+  <si>
+    <t>Temperature</t>
+  </si>
+  <si>
+    <t>Chl-a &amp; fDOM</t>
+  </si>
+  <si>
+    <t>4x t-chain + bottom DO &amp; CTD (4x TGR + 1x miniDOT + 1x RDI600 + 1xCTD)</t>
+  </si>
+  <si>
+    <t>1x bottom ADCP (1x RD1000)</t>
+  </si>
+  <si>
+    <t>4x t-chain + bottom T/DO (4x SBE / 4x RBRduet + 1x miniDOT + 1xRDI)</t>
+  </si>
+  <si>
+    <t>1x bottom CTD, miniPAR, RBR &amp; ADCP (1x CTD, 1xminiPAR, 1xRBRsolo,  RD1200)</t>
+  </si>
+  <si>
+    <t>1x bottom miniPAR, RBR &amp; ADCP (1x miniPAR, 1xRBRsolo, 1xAquadopp)</t>
+  </si>
+  <si>
+    <t>1x bottom miniPAR, RBR &amp; ADCP (1x miniPAR, 1xRBRsolo (2-codes though), 1xRDI1200)</t>
+  </si>
+  <si>
+    <t>1x bottom RBR &amp; ADCP (1xRBRsolo, 1xAquadoppHR)</t>
+  </si>
+  <si>
+    <t>2018-11  - 2019-09</t>
+  </si>
+  <si>
+    <t>1x bottom deployment (1x HOBO-U26)</t>
+  </si>
+  <si>
+    <t>2004-07 - 2005-07</t>
+  </si>
+  <si>
+    <t>1x bottom + 1x water column sensros (2xSBE + 1xAQD)</t>
+  </si>
+  <si>
+    <t>2005-02 - 2005-04</t>
+  </si>
+  <si>
+    <t>1x bottom + 1x water column sensros (2xSBE + 1xRDI)</t>
+  </si>
+  <si>
+    <t>2004-08 - 2005-06</t>
+  </si>
+  <si>
+    <t>1x bottom + 2x water column sensros (3xSBE + 1xRDI)</t>
+  </si>
+  <si>
+    <t>3 levels from Apr 2018 - Aug 2018</t>
+  </si>
+  <si>
+    <t>2x levels (surface and bottom T,S,DO)</t>
+  </si>
+  <si>
+    <t>3x levels (3x T,S and 1x bottom DO)</t>
+  </si>
+  <si>
+    <t>2008-2013</t>
+  </si>
+  <si>
+    <t>11x t-chain (hourly resolution + 2x salinity)</t>
+  </si>
+  <si>
+    <t>8x t-chain</t>
+  </si>
+  <si>
+    <t>13x t-chain</t>
+  </si>
+  <si>
+    <t>2010-11 - 2010-12</t>
+  </si>
+  <si>
+    <t>6x t-chain (6x SBE39)</t>
+  </si>
+  <si>
+    <t>2010-11 - 2011-01</t>
+  </si>
+  <si>
+    <t>AIMS</t>
+  </si>
+  <si>
+    <t>2013-2015</t>
+  </si>
+  <si>
+    <t>1x thermistor</t>
   </si>
 </sst>
 </file>
@@ -546,7 +645,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -593,22 +692,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -634,8 +722,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
@@ -937,1103 +1028,1243 @@
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>11</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="F2" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="F6" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C22">
+        <v>137</v>
+      </c>
+      <c r="C22" s="11">
         <v>6147030</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
-        <v>123</v>
-      </c>
-      <c r="G22" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" t="s">
-        <v>124</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C23">
+        <v>137</v>
+      </c>
+      <c r="C23" s="11">
         <v>6147031</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
-        <v>125</v>
-      </c>
-      <c r="G23" t="s">
-        <v>125</v>
-      </c>
-      <c r="H23" t="s">
-        <v>124</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E23" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C24">
+        <v>137</v>
+      </c>
+      <c r="C24" s="11">
         <v>6147034</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C25">
+        <v>137</v>
+      </c>
+      <c r="C25" s="11">
         <v>6147035</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" t="s">
-        <v>126</v>
-      </c>
-      <c r="G25" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" t="s">
-        <v>124</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="E25" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C26">
+        <v>137</v>
+      </c>
+      <c r="C26" s="11">
         <v>6147032</v>
       </c>
-      <c r="D26" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G26" t="s">
-        <v>133</v>
-      </c>
-      <c r="H26" t="s">
-        <v>134</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D26" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C27">
+        <v>137</v>
+      </c>
+      <c r="C27" s="11">
         <v>6147033</v>
       </c>
-      <c r="D27" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" t="s">
-        <v>29</v>
-      </c>
-      <c r="F27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G27" t="s">
-        <v>135</v>
-      </c>
-      <c r="H27" t="s">
-        <v>134</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D27" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C28">
+        <v>137</v>
+      </c>
+      <c r="C28" s="11">
         <v>6147036</v>
       </c>
-      <c r="D28" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" t="s">
-        <v>29</v>
-      </c>
-      <c r="F28" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" t="s">
-        <v>136</v>
-      </c>
-      <c r="H28" t="s">
-        <v>134</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D28" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29">
+        <v>137</v>
+      </c>
+      <c r="C29" s="11">
         <v>6147037</v>
       </c>
-      <c r="D29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" t="s">
-        <v>137</v>
-      </c>
-      <c r="G29" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" t="s">
-        <v>134</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D29" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C30">
+        <v>137</v>
+      </c>
+      <c r="C30" s="11">
         <v>6140269</v>
       </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" t="s">
-        <v>23</v>
+      <c r="D30" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>24</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C31">
+        <v>137</v>
+      </c>
+      <c r="C31" s="11">
         <v>6140266</v>
       </c>
-      <c r="D31" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>138</v>
-      </c>
-      <c r="G31" t="s">
-        <v>138</v>
-      </c>
-      <c r="H31" t="s">
-        <v>134</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D31" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32">
+        <v>137</v>
+      </c>
+      <c r="C32" s="11">
         <v>6140265</v>
       </c>
-      <c r="D32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" t="s">
-        <v>14</v>
+      <c r="D32" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33">
+        <v>137</v>
+      </c>
+      <c r="C33" s="11">
         <v>6140281</v>
       </c>
-      <c r="D33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" t="s">
-        <v>14</v>
-      </c>
-      <c r="F33" t="s">
-        <v>139</v>
-      </c>
-      <c r="G33" t="s">
-        <v>139</v>
-      </c>
-      <c r="H33" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D33" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34">
+        <v>137</v>
+      </c>
+      <c r="C34" s="11">
         <v>6140267</v>
       </c>
-      <c r="D34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" t="s">
-        <v>14</v>
+      <c r="D34" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C35">
+        <v>137</v>
+      </c>
+      <c r="C35" s="11">
         <v>6140268</v>
       </c>
-      <c r="D35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E35" t="s">
-        <v>14</v>
+      <c r="D35" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>15</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C36">
+        <v>137</v>
+      </c>
+      <c r="C36" s="11">
         <v>6140254</v>
       </c>
-      <c r="D36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" t="s">
-        <v>32</v>
-      </c>
-      <c r="F36" t="s">
-        <v>140</v>
-      </c>
-      <c r="G36" t="s">
-        <v>140</v>
-      </c>
-      <c r="H36" t="s">
-        <v>141</v>
-      </c>
-      <c r="I36" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D36" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C37">
+        <v>137</v>
+      </c>
+      <c r="C37" s="11">
         <v>6147038</v>
       </c>
-      <c r="D37" t="s">
-        <v>65</v>
-      </c>
-      <c r="E37" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" t="s">
-        <v>142</v>
-      </c>
-      <c r="G37" t="s">
-        <v>142</v>
-      </c>
-      <c r="H37" t="s">
-        <v>141</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="D37" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C38">
+        <v>137</v>
+      </c>
+      <c r="C38" s="11">
         <v>6140305</v>
       </c>
-      <c r="D38" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" t="s">
-        <v>29</v>
+      <c r="D38" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>30</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="H38" t="s">
+        <v>141</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="I38" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>135</v>
+      </c>
       <c r="I39" s="8" t="s">
-        <v>151</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2043,664 +2274,1955 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{114A48C8-9611-D74F-B2B0-D2018621AE76}">
-  <dimension ref="B1:H62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A514C5CE-2A39-E241-B87A-E76BA54CDEA5}">
+  <dimension ref="A1:L65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="10" width="19.6640625" customWidth="1"/>
+    <col min="11" max="11" width="71.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B1" t="s">
+    <row r="1" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2022</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I8" t="s">
+        <v>109</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I15" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C1">
+      <c r="D21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22">
         <v>6147030</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D22" t="s">
         <v>48</v>
       </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H22" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23">
+        <v>6147031</v>
+      </c>
+      <c r="D23" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G23" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I23" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" t="s">
+        <v>147</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24">
+        <v>6147034</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H24" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" t="s">
+        <v>148</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K24" t="s">
+        <v>147</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C25">
+        <v>6147035</v>
+      </c>
+      <c r="D25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s">
+        <v>122</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K25" t="s">
+        <v>147</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26">
+        <v>6147032</v>
+      </c>
+      <c r="D26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" t="s">
         <v>123</v>
       </c>
-      <c r="H1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C2">
-        <v>6147031</v>
-      </c>
-      <c r="D2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C3">
-        <v>6147034</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C4">
-        <v>6147035</v>
-      </c>
-      <c r="D4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" t="s">
+        <v>123</v>
+      </c>
+      <c r="I26" t="s">
+        <v>123</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K26" t="s">
+        <v>149</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27">
+        <v>6147033</v>
+      </c>
+      <c r="D27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" t="s">
+        <v>123</v>
+      </c>
+      <c r="H27" t="s">
+        <v>123</v>
+      </c>
+      <c r="I27" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" t="s">
+        <v>149</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C28">
+        <v>6147036</v>
+      </c>
+      <c r="D28" t="s">
+        <v>54</v>
+      </c>
+      <c r="E28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" t="s">
         <v>126</v>
       </c>
-      <c r="H4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6">
-        <v>6147032</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C7">
-        <v>6147033</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>129</v>
-      </c>
-      <c r="G7" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C8">
-        <v>6147036</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="G28" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" t="s">
+        <v>126</v>
+      </c>
+      <c r="I28" t="s">
+        <v>126</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K28" t="s">
+        <v>149</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29">
+        <v>6147037</v>
+      </c>
+      <c r="D29" t="s">
         <v>55</v>
       </c>
-      <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>131</v>
-      </c>
-      <c r="H8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C9">
-        <v>6147037</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="E29" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" t="s">
+        <v>126</v>
+      </c>
+      <c r="G29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" t="s">
+        <v>126</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K29" t="s">
+        <v>149</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30">
+        <v>6140269</v>
+      </c>
+      <c r="D30" t="s">
         <v>56</v>
       </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>132</v>
-      </c>
-      <c r="H9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" t="s">
+      <c r="E30" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" t="s">
+        <v>150</v>
+      </c>
+      <c r="I30" t="s">
+        <v>150</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" t="s">
+        <v>151</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31">
+        <v>6140266</v>
+      </c>
+      <c r="D31" t="s">
         <v>57</v>
       </c>
-      <c r="C12">
-        <v>6147032</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C13">
-        <v>6147033</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C14">
-        <v>6147036</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" t="s">
-        <v>136</v>
-      </c>
-      <c r="H14" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C15">
-        <v>6147037</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="E31" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" t="s">
+        <v>152</v>
+      </c>
+      <c r="G31" t="s">
+        <v>152</v>
+      </c>
+      <c r="H31" t="s">
+        <v>152</v>
+      </c>
+      <c r="I31" t="s">
+        <v>152</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K31" t="s">
+        <v>149</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="H15" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C16">
-        <v>6140269</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C32">
+        <v>6140265</v>
+      </c>
+      <c r="D32" t="s">
         <v>58</v>
       </c>
-      <c r="E16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C17">
-        <v>6140266</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="E32" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G32" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" t="s">
+        <v>153</v>
+      </c>
+      <c r="I32" t="s">
+        <v>153</v>
+      </c>
+      <c r="J32" t="s">
+        <v>153</v>
+      </c>
+      <c r="K32" t="s">
+        <v>151</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C33">
+        <v>6140281</v>
+      </c>
+      <c r="D33" t="s">
         <v>59</v>
       </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>138</v>
-      </c>
-      <c r="H17" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C18">
-        <v>6140265</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="E33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" t="s">
+        <v>154</v>
+      </c>
+      <c r="G33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" t="s">
+        <v>154</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K33" t="s">
+        <v>149</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34">
+        <v>6140267</v>
+      </c>
+      <c r="D34" t="s">
         <v>60</v>
       </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C19">
-        <v>6140281</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" t="s">
+        <v>153</v>
+      </c>
+      <c r="G34" t="s">
+        <v>153</v>
+      </c>
+      <c r="H34" t="s">
+        <v>153</v>
+      </c>
+      <c r="I34" t="s">
+        <v>153</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K34" t="s">
+        <v>151</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35">
+        <v>6140268</v>
+      </c>
+      <c r="D35" t="s">
         <v>61</v>
       </c>
-      <c r="E19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s">
-        <v>139</v>
-      </c>
-      <c r="H19" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C20">
-        <v>6140267</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C21">
-        <v>6140268</v>
-      </c>
-      <c r="D21" t="s">
-        <v>63</v>
-      </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C22">
-        <v>6140254</v>
-      </c>
-      <c r="D22" t="s">
-        <v>64</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>140</v>
-      </c>
-      <c r="H22" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C23">
-        <v>6147038</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E35" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" t="s">
+        <v>153</v>
+      </c>
+      <c r="G35" t="s">
+        <v>153</v>
+      </c>
+      <c r="H35" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35" t="s">
+        <v>153</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="K35" t="s">
+        <v>151</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" t="s">
         <v>65</v>
       </c>
-      <c r="E23" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" t="s">
-        <v>142</v>
-      </c>
-      <c r="H23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C24">
-        <v>6140305</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="C36" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H24" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26" t="s">
+      <c r="D36" t="s">
         <v>67</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E36" t="s">
         <v>68</v>
       </c>
-      <c r="D26" t="s">
+      <c r="G36" t="s">
+        <v>109</v>
+      </c>
+      <c r="I36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E26" t="s">
+      <c r="D37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B38" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C27" t="s">
+      <c r="C38" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="D27" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D38" t="s">
+        <v>72</v>
+      </c>
+      <c r="E38" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" t="s">
+        <v>166</v>
+      </c>
+      <c r="K38" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B29" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="C39" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D39" t="s">
         <v>74</v>
       </c>
-      <c r="E29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C30" t="s">
+      <c r="G39" t="s">
+        <v>168</v>
+      </c>
+      <c r="I39" t="s">
+        <v>168</v>
+      </c>
+      <c r="K39" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" t="s">
+        <v>70</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
         <v>75</v>
       </c>
-      <c r="D30" t="s">
+      <c r="I40" t="s">
+        <v>170</v>
+      </c>
+      <c r="K40" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D31" t="s">
+      <c r="G41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I41" t="s">
+        <v>172</v>
+      </c>
+      <c r="K41" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="D32" t="s">
+      <c r="C42" s="12" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B34" t="s">
+      <c r="D42" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" t="s">
+        <v>24</v>
+      </c>
+      <c r="G42" t="s">
+        <v>174</v>
+      </c>
+      <c r="K42" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B43" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B44" t="s">
+        <v>77</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="K44" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" t="s">
         <v>79</v>
       </c>
-      <c r="C34" t="s">
+      <c r="E45" t="s">
+        <v>15</v>
+      </c>
+      <c r="K45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>77</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D34" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D35" t="s">
+      <c r="D46" t="s">
+        <v>81</v>
+      </c>
+      <c r="E46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B47" t="s">
         <v>77</v>
       </c>
-      <c r="E35" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D36" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D37" t="s">
-        <v>81</v>
-      </c>
-      <c r="E37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C39" t="s">
+      <c r="C47" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" t="s">
         <v>82</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E39" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D40" t="s">
+      <c r="D48" t="s">
         <v>84</v>
       </c>
-      <c r="E40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C41" t="s">
+      <c r="E48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G48" t="s">
+        <v>177</v>
+      </c>
+      <c r="I48" t="s">
+        <v>177</v>
+      </c>
+      <c r="K48" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" t="s">
+        <v>77</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" t="s">
         <v>85</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E49" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" t="s">
+        <v>177</v>
+      </c>
+      <c r="I49" t="s">
+        <v>177</v>
+      </c>
+      <c r="K49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B50" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" t="s">
         <v>86</v>
       </c>
-      <c r="E41" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C42" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>177</v>
+      </c>
+      <c r="I50" t="s">
+        <v>177</v>
+      </c>
+      <c r="K50" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B51" t="s">
         <v>87</v>
       </c>
-      <c r="E42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C43" t="s">
-        <v>85</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="C51" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="E43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B45" t="s">
+      <c r="D51" t="s">
         <v>89</v>
       </c>
-      <c r="C45" t="s">
+      <c r="I51" t="s">
+        <v>181</v>
+      </c>
+      <c r="K51" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" t="s">
+        <v>87</v>
+      </c>
+      <c r="C52" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D52" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C46" t="s">
+      <c r="I52" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B53" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D53" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C47" t="s">
+      <c r="E53" t="s">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D54" t="s">
         <v>95</v>
       </c>
-      <c r="E47" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C48" t="s">
+      <c r="I54" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B55" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D55" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C49" t="s">
+      <c r="I55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B56" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D56" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C50" t="s">
+      <c r="I56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D57" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="51" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C51" t="s">
+      <c r="I57" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B58" t="s">
+        <v>87</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D58" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="52" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C52" t="s">
+      <c r="E58" t="s">
+        <v>28</v>
+      </c>
+      <c r="I58" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D59" t="s">
         <v>105</v>
       </c>
-      <c r="E52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C53" t="s">
+      <c r="I59" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
+        <v>87</v>
+      </c>
+      <c r="C60" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D60" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="54" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C54" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="56" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C56" t="s">
-        <v>110</v>
-      </c>
-      <c r="D56" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="58" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="E58" t="s">
-        <v>27</v>
-      </c>
-      <c r="G58" t="s">
-        <v>144</v>
-      </c>
-      <c r="H58" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="59" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C59" t="s">
-        <v>112</v>
-      </c>
-      <c r="E59" t="s">
-        <v>27</v>
-      </c>
-      <c r="G59" t="s">
-        <v>144</v>
-      </c>
-      <c r="H59" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C60" t="s">
-        <v>112</v>
-      </c>
-      <c r="E60" t="s">
-        <v>27</v>
-      </c>
-      <c r="G60" t="s">
-        <v>144</v>
-      </c>
-      <c r="H60" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="61" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C61" t="s">
-        <v>112</v>
-      </c>
-      <c r="E61" t="s">
-        <v>27</v>
-      </c>
-      <c r="G61" t="s">
-        <v>144</v>
-      </c>
-      <c r="H61" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="62" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C62" t="s">
-        <v>112</v>
-      </c>
-      <c r="E62" t="s">
-        <v>27</v>
-      </c>
-      <c r="G62" t="s">
-        <v>144</v>
-      </c>
-      <c r="H62" t="s">
-        <v>145</v>
+      <c r="I60" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" t="s">
+        <v>184</v>
+      </c>
+      <c r="C61" s="12">
+        <v>12055</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I61" t="s">
+        <v>185</v>
+      </c>
+      <c r="K61" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B62" t="s">
+        <v>184</v>
+      </c>
+      <c r="C62" s="12">
+        <v>12057</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I62" t="s">
+        <v>185</v>
+      </c>
+      <c r="K62" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B63" t="s">
+        <v>184</v>
+      </c>
+      <c r="C63" s="12">
+        <v>13215</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I63" t="s">
+        <v>185</v>
+      </c>
+      <c r="K63" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B64" t="s">
+        <v>184</v>
+      </c>
+      <c r="C64" s="12">
+        <v>13355</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I64" t="s">
+        <v>185</v>
+      </c>
+      <c r="K64" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B65" t="s">
+        <v>184</v>
+      </c>
+      <c r="C65" s="12">
+        <v>14116</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="I65" t="s">
+        <v>185</v>
+      </c>
+      <c r="K65" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/tables/sensor_summary.xlsx
+++ b/tables/sensor_summary.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/AED5/AED Dropbox/AED_Cockburn_db/SEAF-CS/csiem-science/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A90B58-9053-9C4B-9163-D6D7772010E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{635A21E6-A1EE-FF4D-8FDE-15F6E989A86C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13520" yWindow="6060" windowWidth="28680" windowHeight="18040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33800" yWindow="4560" windowWidth="28680" windowHeight="18040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="light" sheetId="1" r:id="rId1"/>
     <sheet name="wq" sheetId="3" r:id="rId2"/>
+    <sheet name="hydro" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="236">
   <si>
     <t>Table</t>
   </si>
@@ -352,6 +353,12 @@
     <t>hillarysish</t>
   </si>
   <si>
+    <t>SPOT-</t>
+  </si>
+  <si>
+    <t>Hilarys</t>
+  </si>
+  <si>
     <t>GK-41870</t>
   </si>
   <si>
@@ -436,6 +443,9 @@
     <t xml:space="preserve">1x bottom PAR deployment </t>
   </si>
   <si>
+    <t>WWMSP9</t>
+  </si>
+  <si>
     <t>WAMSI-WWMSP2-SGREST</t>
   </si>
   <si>
@@ -587,6 +597,144 @@
   </si>
   <si>
     <t>1x thermistor</t>
+  </si>
+  <si>
+    <t>Hydrodynamics</t>
+  </si>
+  <si>
+    <t>3 deployments (RDI600)</t>
+  </si>
+  <si>
+    <t>4 deployments (RDI1000)</t>
+  </si>
+  <si>
+    <t>5 deployments (RDI600 then RDI1000)</t>
+  </si>
+  <si>
+    <t>4 deployments (RDI1200)</t>
+  </si>
+  <si>
+    <t>4 deployments (Aquadopp)</t>
+  </si>
+  <si>
+    <t>1 x RBRsolo (2Hz)</t>
+  </si>
+  <si>
+    <t>2 x RBRsolo (2Hz)</t>
+  </si>
+  <si>
+    <t>3 x RBRsolo (2Hz)</t>
+  </si>
+  <si>
+    <t>4 x RBRsolo (2Hz)</t>
+  </si>
+  <si>
+    <t>5 x RBRsolo (2Hz)</t>
+  </si>
+  <si>
+    <t>WAMSI-WWMSP5-AWAC</t>
+  </si>
+  <si>
+    <t>1x bottom ADCP (RDI600)</t>
+  </si>
+  <si>
+    <t>1x bottom ADCP (Nortek)</t>
+  </si>
+  <si>
+    <t>Aquadopp</t>
+  </si>
+  <si>
+    <t>1x bottom ADCP (RDI1200)</t>
+  </si>
+  <si>
+    <t>ADV</t>
+  </si>
+  <si>
+    <t>UWA-OI-RUIZ</t>
+  </si>
+  <si>
+    <t>UWA-OI-WAWAVES</t>
+  </si>
+  <si>
+    <t>Waverider</t>
+  </si>
+  <si>
+    <t>hillarys</t>
+  </si>
+  <si>
+    <t>CSIRO-SRFNE</t>
+  </si>
+  <si>
+    <t>2006-winter / 2007-summer</t>
+  </si>
+  <si>
+    <t>ADCP / ADV</t>
+  </si>
+  <si>
+    <t>WAVE</t>
+  </si>
+  <si>
+    <t>PB-A</t>
+  </si>
+  <si>
+    <t>parmelia A</t>
+  </si>
+  <si>
+    <t>PB-B</t>
+  </si>
+  <si>
+    <t>parmelia B</t>
+  </si>
+  <si>
+    <t>SB-A</t>
+  </si>
+  <si>
+    <t>success A</t>
+  </si>
+  <si>
+    <t>SB-B</t>
+  </si>
+  <si>
+    <t>success B</t>
+  </si>
+  <si>
+    <t>2 deployments (Nortek ADV)</t>
+  </si>
+  <si>
+    <t>1 deployments (AquadoppHR) (3 deployments for RBR)</t>
+  </si>
+  <si>
+    <t>WAMSI-WWMSP9-ADV</t>
+  </si>
+  <si>
+    <t>S01 (westport)</t>
+  </si>
+  <si>
+    <t>S02 (central)</t>
+  </si>
+  <si>
+    <t>2012-12 - 2013-12</t>
+  </si>
+  <si>
+    <t>2013-01 - 2013-02</t>
+  </si>
+  <si>
+    <t>2013-01 - 2013-09</t>
+  </si>
+  <si>
+    <t>JPPL-AWAC</t>
+  </si>
+  <si>
+    <t>S01a-d</t>
+  </si>
+  <si>
+    <t>S02a-d</t>
+  </si>
+  <si>
+    <t>4x bottom deployments (Nortek AWAC)</t>
+  </si>
+  <si>
+    <t>JPPL</t>
   </si>
 </sst>
 </file>
@@ -696,7 +844,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -723,10 +871,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1046,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1066,16 +1229,16 @@
         <v>15</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1095,16 +1258,16 @@
         <v>15</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1124,16 +1287,16 @@
         <v>15</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1153,13 +1316,13 @@
         <v>24</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I5" s="5" t="s">
         <v>5</v>
@@ -1182,13 +1345,13 @@
         <v>24</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>5</v>
@@ -1205,19 +1368,19 @@
         <v>27</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I7" s="5" t="s">
         <v>5</v>
@@ -1234,22 +1397,22 @@
         <v>29</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1269,13 +1432,13 @@
         <v>33</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I9" s="5" t="s">
         <v>6</v>
@@ -1292,22 +1455,22 @@
         <v>35</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1321,22 +1484,22 @@
         <v>36</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1350,22 +1513,22 @@
         <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1379,22 +1542,22 @@
         <v>38</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1408,22 +1571,22 @@
         <v>39</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1437,19 +1600,19 @@
         <v>40</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I15" s="5" t="s">
         <v>4</v>
@@ -1466,19 +1629,19 @@
         <v>42</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I16" s="5" t="s">
         <v>7</v>
@@ -1495,19 +1658,19 @@
         <v>43</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>7</v>
@@ -1524,19 +1687,19 @@
         <v>44</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I18" s="5" t="s">
         <v>7</v>
@@ -1553,19 +1716,19 @@
         <v>45</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>7</v>
@@ -1582,19 +1745,19 @@
         <v>46</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I20" s="5" t="s">
         <v>7</v>
@@ -1611,19 +1774,19 @@
         <v>47</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>7</v>
@@ -1634,9 +1797,9 @@
         <v>2</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C22" s="11">
+        <v>140</v>
+      </c>
+      <c r="C22" s="14">
         <v>6147030</v>
       </c>
       <c r="D22" s="10" t="s">
@@ -1646,16 +1809,16 @@
         <v>15</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1663,9 +1826,9 @@
         <v>2</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C23" s="11">
+        <v>140</v>
+      </c>
+      <c r="C23" s="14">
         <v>6147031</v>
       </c>
       <c r="D23" s="10" t="s">
@@ -1675,16 +1838,16 @@
         <v>15</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1692,9 +1855,9 @@
         <v>2</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C24" s="11">
+        <v>140</v>
+      </c>
+      <c r="C24" s="14">
         <v>6147034</v>
       </c>
       <c r="D24" s="10" t="s">
@@ -1704,16 +1867,16 @@
         <v>15</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1721,9 +1884,9 @@
         <v>2</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C25" s="11">
+        <v>140</v>
+      </c>
+      <c r="C25" s="14">
         <v>6147035</v>
       </c>
       <c r="D25" s="10" t="s">
@@ -1733,16 +1896,16 @@
         <v>15</v>
       </c>
       <c r="F25" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="H25" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="10" t="s">
-        <v>120</v>
-      </c>
       <c r="I25" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1750,9 +1913,9 @@
         <v>2</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" s="11">
+        <v>140</v>
+      </c>
+      <c r="C26" s="14">
         <v>6147032</v>
       </c>
       <c r="D26" s="10" t="s">
@@ -1762,16 +1925,16 @@
         <v>24</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1779,9 +1942,9 @@
         <v>2</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C27" s="11">
+        <v>140</v>
+      </c>
+      <c r="C27" s="14">
         <v>6147033</v>
       </c>
       <c r="D27" s="10" t="s">
@@ -1791,16 +1954,16 @@
         <v>30</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1808,9 +1971,9 @@
         <v>2</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C28" s="11">
+        <v>140</v>
+      </c>
+      <c r="C28" s="14">
         <v>6147036</v>
       </c>
       <c r="D28" s="10" t="s">
@@ -1820,16 +1983,16 @@
         <v>30</v>
       </c>
       <c r="F28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>124</v>
-      </c>
       <c r="I28" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1837,9 +2000,9 @@
         <v>2</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C29" s="11">
+        <v>140</v>
+      </c>
+      <c r="C29" s="14">
         <v>6147037</v>
       </c>
       <c r="D29" s="10" t="s">
@@ -1849,16 +2012,16 @@
         <v>24</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1866,9 +2029,9 @@
         <v>2</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="11">
+        <v>140</v>
+      </c>
+      <c r="C30" s="14">
         <v>6140269</v>
       </c>
       <c r="D30" s="10" t="s">
@@ -1878,16 +2041,16 @@
         <v>24</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1895,9 +2058,9 @@
         <v>2</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C31" s="11">
+        <v>140</v>
+      </c>
+      <c r="C31" s="14">
         <v>6140266</v>
       </c>
       <c r="D31" s="10" t="s">
@@ -1907,16 +2070,16 @@
         <v>15</v>
       </c>
       <c r="F31" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1924,9 +2087,9 @@
         <v>2</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C32" s="11">
+        <v>140</v>
+      </c>
+      <c r="C32" s="14">
         <v>6140265</v>
       </c>
       <c r="D32" s="10" t="s">
@@ -1936,16 +2099,16 @@
         <v>15</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1953,9 +2116,9 @@
         <v>2</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C33" s="11">
+        <v>140</v>
+      </c>
+      <c r="C33" s="14">
         <v>6140281</v>
       </c>
       <c r="D33" s="10" t="s">
@@ -1965,16 +2128,16 @@
         <v>15</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -1982,9 +2145,9 @@
         <v>2</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C34" s="11">
+        <v>140</v>
+      </c>
+      <c r="C34" s="14">
         <v>6140267</v>
       </c>
       <c r="D34" s="10" t="s">
@@ -1994,16 +2157,16 @@
         <v>15</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2011,9 +2174,9 @@
         <v>2</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C35" s="11">
+        <v>140</v>
+      </c>
+      <c r="C35" s="14">
         <v>6140268</v>
       </c>
       <c r="D35" s="10" t="s">
@@ -2023,16 +2186,16 @@
         <v>15</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,9 +2203,9 @@
         <v>2</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C36" s="11">
+        <v>140</v>
+      </c>
+      <c r="C36" s="14">
         <v>6140254</v>
       </c>
       <c r="D36" s="10" t="s">
@@ -2052,16 +2215,16 @@
         <v>33</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2069,9 +2232,9 @@
         <v>2</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C37" s="11">
+        <v>140</v>
+      </c>
+      <c r="C37" s="14">
         <v>6147038</v>
       </c>
       <c r="D37" s="10" t="s">
@@ -2081,16 +2244,16 @@
         <v>33</v>
       </c>
       <c r="F37" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2098,9 +2261,9 @@
         <v>2</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C38" s="11">
+        <v>140</v>
+      </c>
+      <c r="C38" s="14">
         <v>6140305</v>
       </c>
       <c r="D38" s="10" t="s">
@@ -2110,16 +2273,16 @@
         <v>30</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2129,26 +2292,26 @@
       <c r="B39" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C39" s="11" t="s">
-        <v>108</v>
+      <c r="C39" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2158,26 +2321,26 @@
       <c r="B40" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="11" t="s">
-        <v>108</v>
+      <c r="C40" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2187,26 +2350,26 @@
       <c r="B41" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C41" s="11" t="s">
-        <v>108</v>
+      <c r="C41" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2216,26 +2379,26 @@
       <c r="B42" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C42" s="11" t="s">
-        <v>108</v>
+      <c r="C42" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E42" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -2245,26 +2408,26 @@
       <c r="B43" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C43" s="11" t="s">
-        <v>108</v>
+      <c r="C43" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E43" s="10" t="s">
         <v>28</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2306,27 +2469,27 @@
         <v>8</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>16</v>
@@ -2341,30 +2504,30 @@
         <v>15</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>16</v>
@@ -2379,30 +2542,30 @@
         <v>15</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>16</v>
@@ -2417,30 +2580,30 @@
         <v>15</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -2455,22 +2618,22 @@
         <v>24</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G5" s="8">
         <v>2022</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>5</v>
@@ -2478,7 +2641,7 @@
     </row>
     <row r="6" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>16</v>
@@ -2493,22 +2656,22 @@
         <v>24</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>5</v>
@@ -2516,7 +2679,7 @@
     </row>
     <row r="7" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>16</v>
@@ -2525,28 +2688,28 @@
         <v>27</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>5</v>
@@ -2554,7 +2717,7 @@
     </row>
     <row r="8" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
@@ -2563,36 +2726,36 @@
         <v>29</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>16</v>
@@ -2607,22 +2770,22 @@
         <v>33</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>6</v>
@@ -2630,7 +2793,7 @@
     </row>
     <row r="10" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>34</v>
@@ -2639,36 +2802,36 @@
         <v>35</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>34</v>
@@ -2677,36 +2840,36 @@
         <v>36</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>34</v>
@@ -2715,36 +2878,36 @@
         <v>37</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>34</v>
@@ -2753,36 +2916,36 @@
         <v>38</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>34</v>
@@ -2791,36 +2954,36 @@
         <v>39</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>34</v>
@@ -2829,28 +2992,28 @@
         <v>40</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>4</v>
@@ -2858,7 +3021,7 @@
     </row>
     <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>41</v>
@@ -2867,28 +3030,28 @@
         <v>42</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>7</v>
@@ -2896,7 +3059,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>41</v>
@@ -2905,28 +3068,28 @@
         <v>43</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>7</v>
@@ -2934,7 +3097,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>41</v>
@@ -2943,28 +3106,28 @@
         <v>44</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>7</v>
@@ -2972,7 +3135,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>41</v>
@@ -2981,28 +3144,28 @@
         <v>45</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>28</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>7</v>
@@ -3010,7 +3173,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>41</v>
@@ -3019,28 +3182,28 @@
         <v>46</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>7</v>
@@ -3048,7 +3211,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>41</v>
@@ -3057,28 +3220,28 @@
         <v>47</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>7</v>
@@ -3086,10 +3249,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C22">
         <v>6147030</v>
@@ -3101,33 +3264,33 @@
         <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K22" t="s">
+        <v>148</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>145</v>
-      </c>
-      <c r="L22" s="5" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C23">
         <v>6147031</v>
@@ -3139,33 +3302,33 @@
         <v>15</v>
       </c>
       <c r="F23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="I23" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K23" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C24">
         <v>6147034</v>
@@ -3177,33 +3340,33 @@
         <v>15</v>
       </c>
       <c r="F24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="I24" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C25">
         <v>6147035</v>
@@ -3215,33 +3378,33 @@
         <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C26">
         <v>6147032</v>
@@ -3253,33 +3416,33 @@
         <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K26" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C27">
         <v>6147033</v>
@@ -3291,33 +3454,33 @@
         <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I27" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K27" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C28">
         <v>6147036</v>
@@ -3329,33 +3492,33 @@
         <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I28" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K28" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C29">
         <v>6147037</v>
@@ -3367,33 +3530,33 @@
         <v>24</v>
       </c>
       <c r="F29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I29" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K29" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C30">
         <v>6140269</v>
@@ -3405,33 +3568,33 @@
         <v>24</v>
       </c>
       <c r="F30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="H30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="I30" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K30" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C31">
         <v>6140266</v>
@@ -3443,33 +3606,33 @@
         <v>15</v>
       </c>
       <c r="F31" t="s">
+        <v>155</v>
+      </c>
+      <c r="G31" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" t="s">
+        <v>155</v>
+      </c>
+      <c r="I31" t="s">
+        <v>155</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="K31" t="s">
         <v>152</v>
       </c>
-      <c r="G31" t="s">
-        <v>152</v>
-      </c>
-      <c r="H31" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" t="s">
-        <v>152</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="K31" t="s">
-        <v>149</v>
-      </c>
       <c r="L31" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C32">
         <v>6140265</v>
@@ -3481,33 +3644,33 @@
         <v>15</v>
       </c>
       <c r="F32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J32" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="K32" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C33">
         <v>6140281</v>
@@ -3519,33 +3682,33 @@
         <v>15</v>
       </c>
       <c r="F33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="H33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I33" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J33" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K33" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C34">
         <v>6140267</v>
@@ -3557,33 +3720,33 @@
         <v>15</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I34" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K34" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C35">
         <v>6140268</v>
@@ -3595,35 +3758,35 @@
         <v>15</v>
       </c>
       <c r="F35" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G35" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H35" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="I35" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K35" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B36" t="s">
         <v>65</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="15" t="s">
         <v>66</v>
       </c>
       <c r="D36" t="s">
@@ -3633,20 +3796,20 @@
         <v>68</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I36" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B37" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="15" t="s">
         <v>69</v>
       </c>
       <c r="D37" t="s">
@@ -3656,20 +3819,20 @@
         <v>68</v>
       </c>
       <c r="G37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I37" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B38" t="s">
         <v>70</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="15" t="s">
         <v>71</v>
       </c>
       <c r="D38" t="s">
@@ -3679,86 +3842,86 @@
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K38" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B39" t="s">
         <v>70</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D39" t="s">
         <v>74</v>
       </c>
       <c r="G39" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I39" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K39" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B40" t="s">
         <v>70</v>
       </c>
-      <c r="C40" s="12" t="s">
+      <c r="C40" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D40" t="s">
         <v>75</v>
       </c>
       <c r="I40" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K40" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B41" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="15" t="s">
         <v>73</v>
       </c>
       <c r="D41" t="s">
         <v>76</v>
       </c>
       <c r="G41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I41" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K41" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B42" t="s">
         <v>77</v>
       </c>
-      <c r="C42" s="12" t="s">
+      <c r="C42" s="15" t="s">
         <v>78</v>
       </c>
       <c r="D42" t="s">
@@ -3768,20 +3931,20 @@
         <v>24</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K42" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="12" t="s">
+      <c r="C43" s="15" t="s">
         <v>78</v>
       </c>
       <c r="D43" t="s">
@@ -3791,17 +3954,17 @@
         <v>24</v>
       </c>
       <c r="K43" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B44" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="12" t="s">
+      <c r="C44" s="15" t="s">
         <v>78</v>
       </c>
       <c r="D44" t="s">
@@ -3811,17 +3974,17 @@
         <v>15</v>
       </c>
       <c r="K44" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B45" t="s">
         <v>77</v>
       </c>
-      <c r="C45" s="12" t="s">
+      <c r="C45" s="15" t="s">
         <v>78</v>
       </c>
       <c r="D45" t="s">
@@ -3831,17 +3994,17 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B46" t="s">
         <v>77</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="15" t="s">
         <v>80</v>
       </c>
       <c r="D46" t="s">
@@ -3853,12 +4016,12 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B47" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C47" s="15" t="s">
         <v>80</v>
       </c>
       <c r="D47" t="s">
@@ -3870,12 +4033,12 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B48" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="12" t="s">
+      <c r="C48" s="15" t="s">
         <v>83</v>
       </c>
       <c r="D48" t="s">
@@ -3885,23 +4048,23 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I48" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K48" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B49" t="s">
         <v>77</v>
       </c>
-      <c r="C49" s="12" t="s">
+      <c r="C49" s="15" t="s">
         <v>83</v>
       </c>
       <c r="D49" t="s">
@@ -3911,23 +4074,23 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I49" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K49" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="12" t="s">
+      <c r="C50" s="15" t="s">
         <v>83</v>
       </c>
       <c r="D50" t="s">
@@ -3937,60 +4100,60 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I50" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K50" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B51" t="s">
         <v>87</v>
       </c>
-      <c r="C51" s="12" t="s">
+      <c r="C51" s="15" t="s">
         <v>88</v>
       </c>
       <c r="D51" t="s">
         <v>89</v>
       </c>
       <c r="I51" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K51" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B52" t="s">
         <v>87</v>
       </c>
-      <c r="C52" s="12" t="s">
+      <c r="C52" s="15" t="s">
         <v>90</v>
       </c>
       <c r="D52" t="s">
         <v>91</v>
       </c>
       <c r="I52" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B53" t="s">
         <v>87</v>
       </c>
-      <c r="C53" s="12" t="s">
+      <c r="C53" s="15" t="s">
         <v>92</v>
       </c>
       <c r="D53" t="s">
@@ -4000,85 +4163,85 @@
         <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B54" t="s">
         <v>87</v>
       </c>
-      <c r="C54" s="12" t="s">
+      <c r="C54" s="15" t="s">
         <v>94</v>
       </c>
       <c r="D54" t="s">
         <v>95</v>
       </c>
       <c r="I54" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B55" t="s">
         <v>87</v>
       </c>
-      <c r="C55" s="12" t="s">
+      <c r="C55" s="15" t="s">
         <v>96</v>
       </c>
       <c r="D55" t="s">
         <v>97</v>
       </c>
       <c r="I55" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B56" t="s">
         <v>87</v>
       </c>
-      <c r="C56" s="12" t="s">
+      <c r="C56" s="15" t="s">
         <v>98</v>
       </c>
       <c r="D56" t="s">
         <v>99</v>
       </c>
       <c r="I56" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B57" t="s">
         <v>87</v>
       </c>
-      <c r="C57" s="12" t="s">
+      <c r="C57" s="15" t="s">
         <v>100</v>
       </c>
       <c r="D57" t="s">
         <v>101</v>
       </c>
       <c r="I57" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="12" t="s">
+      <c r="C58" s="15" t="s">
         <v>102</v>
       </c>
       <c r="D58" t="s">
@@ -4088,144 +4251,1167 @@
         <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B59" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="12" t="s">
+      <c r="C59" s="15" t="s">
         <v>104</v>
       </c>
       <c r="D59" t="s">
         <v>105</v>
       </c>
       <c r="I59" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B60" t="s">
         <v>87</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="C60" s="15" t="s">
         <v>106</v>
       </c>
       <c r="D60" t="s">
         <v>107</v>
       </c>
       <c r="I60" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B61" t="s">
-        <v>184</v>
-      </c>
-      <c r="C61" s="12">
+        <v>187</v>
+      </c>
+      <c r="C61" s="15">
         <v>12055</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I61" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K61" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B62" t="s">
-        <v>184</v>
-      </c>
-      <c r="C62" s="12">
+        <v>187</v>
+      </c>
+      <c r="C62" s="15">
         <v>12057</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I62" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K62" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
-      </c>
-      <c r="C63" s="12">
+        <v>187</v>
+      </c>
+      <c r="C63" s="15">
         <v>13215</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I63" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K63" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
-      </c>
-      <c r="C64" s="12">
+        <v>187</v>
+      </c>
+      <c r="C64" s="15">
         <v>13355</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I64" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K64" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B65" t="s">
-        <v>184</v>
-      </c>
-      <c r="C65" s="12">
+        <v>187</v>
+      </c>
+      <c r="C65" s="15">
         <v>14116</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="I65" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K65" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3113B9DF-6895-6848-8B2F-559868DD54F0}">
+  <dimension ref="A1:I35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="15.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="21.1640625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="20.1640625" style="13" customWidth="1"/>
+    <col min="8" max="8" width="60.33203125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="30.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="8">
+        <v>2023</v>
+      </c>
+      <c r="G2" s="8">
+        <v>2023</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="8">
+        <v>2023</v>
+      </c>
+      <c r="G3" s="8">
+        <v>2023</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="8">
+        <v>2023</v>
+      </c>
+      <c r="G4" s="8">
+        <v>2023</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="8">
+        <v>2023</v>
+      </c>
+      <c r="G5" s="8">
+        <v>2023</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="8">
+        <v>2022</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2022</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2022</v>
+      </c>
+      <c r="G12" s="8">
+        <v>2022</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="8"/>
+      <c r="G16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H30" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="H34" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>